--- a/output/pdf_financials_xlsx/GSTM.xlsx
+++ b/output/pdf_financials_xlsx/GSTM.xlsx
@@ -2740,16 +2740,16 @@
         <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.150575</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>0.122288</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>0.007322</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.001393</v>
       </c>
     </row>
     <row r="104">
@@ -2806,16 +2806,16 @@
         <v>0</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.011423</v>
+        <v>-0.161998</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.030698</v>
+        <v>0.09159</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.118991</v>
+        <v>-0.111669</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.017226</v>
+        <v>0.015833</v>
       </c>
     </row>
     <row r="107">
@@ -3070,16 +3070,16 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.319203</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-1.937908</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-1.523832</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-1.564559</v>
       </c>
     </row>
     <row r="119">
@@ -3647,7 +3647,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -5183,7 +5187,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -5409,7 +5417,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -7710,7 +7722,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GSTM.xlsx
+++ b/output/pdf_financials_xlsx/GSTM.xlsx
@@ -675,10 +675,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.018036</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.028896</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1031,10 +1031,10 @@
         <v>-1.869605</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.679598</v>
+        <v>-0.697634</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.446346</v>
+        <v>-0.475242</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.008627</v>
@@ -1075,10 +1075,10 @@
         <v>-1.846911</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.597094</v>
+        <v>-0.61513</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.378437</v>
+        <v>-0.407333</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.999565</v>
@@ -1196,7 +1196,7 @@
         <v>0.124136</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.861351</v>
       </c>
     </row>
     <row r="35">
@@ -1240,7 +1240,7 @@
         <v>0.124136</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.861351</v>
       </c>
     </row>
     <row r="37">
@@ -1504,7 +1504,7 @@
         <v>0.089865</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.883709</v>
+        <v>0.022358</v>
       </c>
     </row>
     <row r="49">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3807,7 +3807,11 @@
           <t>Reclamation deposits (Note 4)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4396,7 +4400,11 @@
           <t>Reclamation deposits (Note 5)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -5380,7 +5388,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -7681,7 +7693,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -8731,7 +8747,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -9205,7 +9221,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">

--- a/output/pdf_financials_xlsx/GSTM.xlsx
+++ b/output/pdf_financials_xlsx/GSTM.xlsx
@@ -565,13 +565,13 @@
         <v>0.299727</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.51494</v>
+        <v>0.519325</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.312427</v>
+        <v>0.330889</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.399826</v>
+        <v>0.417826</v>
       </c>
     </row>
     <row r="8">
@@ -2699,13 +2699,13 @@
         <v>-0.037305</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.026367</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.015361</v>
       </c>
     </row>
     <row r="102">
@@ -2809,13 +2809,13 @@
         <v>-0.161998</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.09159</v>
+        <v>0.117957</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-0.111669</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.015833</v>
+        <v>0.000472</v>
       </c>
     </row>
     <row r="107">
@@ -5119,7 +5119,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -5552,7 +5556,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -8320,7 +8328,11 @@
           <t>Director’s fees (Note 8)</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
